--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://healthri-my.sharepoint.com/personal/hannah_neikes_health-ri_nl/Documents/Documenten/GitHub/health-ri-metadata/Formalisation(shacl)/Core/SHACL_pipeline_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{67D697DE-5446-C941-BDB7-13D5AA62327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81523C56-7F14-4EF5-BCC4-721D6079AD37}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{67D697DE-5446-C941-BDB7-13D5AA62327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{627EBF16-DB06-468F-A08A-68D42C7799C5}"/>
   <bookViews>
-    <workbookView xWindow="4875" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-12576" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prefixes" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="209">
   <si>
     <t>PREFIX</t>
   </si>
@@ -688,6 +688,9 @@
   </si>
   <si>
     <t>xsd:nonNegativeInteger</t>
+  </si>
+  <si>
+    <t>http://data.health-ri.nl/core/p2/RightsStatementShape</t>
   </si>
 </sst>
 </file>
@@ -1826,6 +1829,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
@@ -2357,7 +2364,7 @@
       </c>
       <c r="B7" s="6">
         <f ca="1">NOW()</f>
-        <v>45916.474714236108</v>
+        <v>45964.687811574076</v>
       </c>
       <c r="F7" s="3"/>
     </row>
@@ -2512,7 +2519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -2771,7 +2778,7 @@
     </row>
     <row r="10" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A10" s="47" t="str">
-        <f t="shared" ref="A10:A31" si="0">CONCATENATE(B10,"#",C10)</f>
+        <f t="shared" ref="A10:A30" si="0">CONCATENATE(B10,"#",C10)</f>
         <v>hri:DistributionShape#dcat:accessURL</v>
       </c>
       <c r="B10" s="51" t="s">
@@ -2871,134 +2878,151 @@
       </c>
     </row>
     <row r="13" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="57"/>
-      <c r="G13" s="64"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-    </row>
-    <row r="14" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>hri:DistributionShape#spdx:checksum</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="63"/>
+      <c r="H13" s="25">
+        <v>1</v>
+      </c>
+      <c r="I13" s="48"/>
+      <c r="M13" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="X13" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y13" s="50" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#spdx:checksum</v>
+        <v>hri:DistributionShape#dcat:compressFormat</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="52" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" s="56" t="s">
-        <v>155</v>
-      </c>
-      <c r="G14" s="63"/>
+      <c r="C14" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="G14" s="64"/>
       <c r="H14" s="25">
         <v>1</v>
       </c>
-      <c r="I14" s="48"/>
-      <c r="M14" s="20" t="s">
-        <v>156</v>
-      </c>
+      <c r="I14" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="67"/>
       <c r="X14" s="50" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="Y14" s="50" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="43.2" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dcat:compressFormat</v>
+        <v>hri:DistributionShape#dct:description</v>
       </c>
       <c r="B15" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="54" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>161</v>
-      </c>
-      <c r="G15" s="64"/>
-      <c r="H15" s="25">
+      <c r="C15" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>163</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="G15" s="63"/>
+      <c r="I15" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="L15" s="66"/>
+      <c r="V15" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="L15" s="67"/>
       <c r="X15" s="50" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y15" s="50" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:description</v>
+        <v>hri:DistributionShape#foaf:page</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="52" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" s="58" t="s">
-        <v>164</v>
-      </c>
-      <c r="G16" s="63"/>
+      <c r="C16" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="57"/>
+      <c r="G16" s="64"/>
       <c r="I16" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="L16" s="66"/>
-      <c r="V16" s="5" t="b">
-        <v>1</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="L16" s="67"/>
       <c r="X16" s="50" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="Y16" s="50" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#foaf:page</v>
+        <v>hri:DistributionShape#dcat:downloadURL</v>
       </c>
       <c r="B17" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="53" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="E17" s="57"/>
-      <c r="G17" s="64"/>
+      <c r="C17" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" s="59"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="25">
+        <v>1</v>
+      </c>
       <c r="I17" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="L17" s="67"/>
+      <c r="L17" s="66"/>
       <c r="X17" s="50" t="s">
         <v>143</v>
       </c>
@@ -3009,26 +3033,28 @@
     <row r="18" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dcat:downloadURL</v>
+        <v>hri:DistributionShape#dct:format</v>
       </c>
       <c r="B18" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" s="59"/>
-      <c r="G18" s="63"/>
+      <c r="C18" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" s="57"/>
+      <c r="G18" s="64">
+        <v>1</v>
+      </c>
       <c r="H18" s="25">
         <v>1</v>
       </c>
       <c r="I18" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="L18" s="66"/>
+      <c r="L18" s="67"/>
       <c r="X18" s="50" t="s">
         <v>143</v>
       </c>
@@ -3036,31 +3062,28 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A19" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:format</v>
+        <v>hri:DistributionShape#dct:language</v>
       </c>
       <c r="B19" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="57"/>
-      <c r="G19" s="64">
-        <v>1</v>
-      </c>
-      <c r="H19" s="25">
-        <v>1</v>
-      </c>
+      <c r="C19" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" s="63"/>
       <c r="I19" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="L19" s="67"/>
+      <c r="L19" s="66"/>
       <c r="X19" s="50" t="s">
         <v>143</v>
       </c>
@@ -3068,28 +3091,31 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:language</v>
+        <v>hri:DistributionShape#dct:license</v>
       </c>
       <c r="B20" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="52" t="s">
-        <v>171</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="G20" s="63"/>
+      <c r="C20" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="61"/>
+      <c r="G20" s="64">
+        <v>1</v>
+      </c>
+      <c r="H20" s="25">
+        <v>1</v>
+      </c>
       <c r="I20" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="L20" s="66"/>
+      <c r="L20" s="67"/>
       <c r="X20" s="50" t="s">
         <v>143</v>
       </c>
@@ -3100,28 +3126,23 @@
     <row r="21" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:license</v>
+        <v>hri:DistributionShape#dct:conformsTo</v>
       </c>
       <c r="B21" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="61"/>
-      <c r="G21" s="64">
-        <v>1</v>
-      </c>
-      <c r="H21" s="25">
-        <v>1</v>
-      </c>
+      <c r="C21" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="58"/>
+      <c r="G21" s="63"/>
       <c r="I21" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="L21" s="67"/>
+      <c r="L21" s="66"/>
       <c r="X21" s="50" t="s">
         <v>143</v>
       </c>
@@ -3132,23 +3153,26 @@
     <row r="22" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:conformsTo</v>
+        <v>hri:DistributionShape#dcat:mediaType</v>
       </c>
       <c r="B22" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="E22" s="58"/>
-      <c r="G22" s="63"/>
+      <c r="C22" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="E22" s="62"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="25">
+        <v>1</v>
+      </c>
       <c r="I22" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="L22" s="66"/>
+      <c r="L22" s="67"/>
       <c r="X22" s="50" t="s">
         <v>143</v>
       </c>
@@ -3159,154 +3183,159 @@
     <row r="23" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dcat:mediaType</v>
+        <v>hri:DistributionShape#dct:modified</v>
       </c>
       <c r="B23" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="E23" s="62"/>
-      <c r="G23" s="64"/>
+      <c r="C23" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>181</v>
+      </c>
+      <c r="E23" s="59"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="25">
         <v>1</v>
       </c>
-      <c r="I23" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="L23" s="67"/>
+      <c r="J23" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="K23" s="66"/>
+      <c r="W23" t="s">
+        <v>206</v>
+      </c>
       <c r="X23" s="50" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y23" s="50" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:modified</v>
+        <v>hri:DistributionShape#dcat:packageFormat</v>
       </c>
       <c r="B24" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="D24" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="E24" s="59"/>
-      <c r="G24" s="63"/>
+      <c r="C24" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="G24" s="64"/>
       <c r="H24" s="25">
         <v>1</v>
       </c>
-      <c r="J24" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="K24" s="66"/>
-      <c r="W24" t="s">
-        <v>206</v>
-      </c>
+      <c r="I24" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="L24" s="67"/>
       <c r="X24" s="50" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="Y24" s="50" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="43.2" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dcat:packageFormat</v>
+        <v>hri:DistributionShape#dct:issued</v>
       </c>
       <c r="B25" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="53" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="G25" s="64"/>
+      <c r="C25" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G25" s="63"/>
       <c r="H25" s="25">
         <v>1</v>
       </c>
-      <c r="I25" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="L25" s="67"/>
+      <c r="J25" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="K25" s="66"/>
+      <c r="W25" t="s">
+        <v>206</v>
+      </c>
       <c r="X25" s="50" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y25" s="50" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:issued</v>
+        <v>hri:DistributionShape#healthdcatap:retentionperiod</v>
       </c>
       <c r="B26" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="G26" s="63"/>
+      <c r="C26" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="E26" s="61"/>
+      <c r="G26" s="64"/>
       <c r="H26" s="25">
         <v>1</v>
       </c>
-      <c r="J26" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="K26" s="66"/>
-      <c r="W26" t="s">
-        <v>206</v>
+      <c r="M26" s="20" t="s">
+        <v>192</v>
       </c>
       <c r="X26" s="50" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Y26" s="50" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A27" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#healthdcatap:retentionperiod</v>
+        <v>hri:DistributionShape#dct:rights</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="E27" s="61"/>
-      <c r="G27" s="64"/>
+      <c r="C27" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="63">
+        <v>1</v>
+      </c>
       <c r="H27" s="25">
         <v>1</v>
       </c>
-      <c r="M27" s="20" t="s">
-        <v>192</v>
+      <c r="I27" s="50"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="X27" s="50" t="s">
         <v>157</v>
@@ -3315,98 +3344,98 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A28" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:rights</v>
+        <v>hri:DistributionShape#adms:status</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="G28" s="63">
-        <v>1</v>
-      </c>
+      <c r="C28" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="G28" s="64"/>
       <c r="H28" s="25">
         <v>1</v>
       </c>
       <c r="I28" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="L28" s="66"/>
+      <c r="L28" s="67"/>
+      <c r="T28" t="s">
+        <v>198</v>
+      </c>
       <c r="X28" s="50" t="s">
         <v>143</v>
       </c>
       <c r="Y28" s="50" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A29" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#adms:status</v>
+        <v>hri:DistributionShape#dcat:temporalResolution</v>
       </c>
       <c r="B29" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="G29" s="64"/>
+      <c r="C29" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="59"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="25">
         <v>1</v>
       </c>
-      <c r="I29" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="L29" s="67"/>
-      <c r="T29" t="s">
-        <v>198</v>
-      </c>
+      <c r="J29" s="66" t="s">
+        <v>202</v>
+      </c>
+      <c r="K29" s="66"/>
       <c r="X29" s="50" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Y29" s="50" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="14.4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A30" s="47" t="str">
         <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dcat:temporalResolution</v>
+        <v>hri:DistributionShape#dct:title</v>
       </c>
       <c r="B30" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="E30" s="59"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="25">
+      <c r="C30" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="G30" s="64">
         <v>1</v>
       </c>
-      <c r="J30" s="66" t="s">
-        <v>202</v>
-      </c>
-      <c r="K30" s="66"/>
+      <c r="I30" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="L30" s="67"/>
+      <c r="V30" s="5" t="b">
+        <v>1</v>
+      </c>
       <c r="X30" s="50" t="s">
         <v>151</v>
       </c>
@@ -3414,42 +3443,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="str">
-        <f t="shared" si="0"/>
-        <v>hri:DistributionShape#dct:title</v>
-      </c>
-      <c r="B31" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="E31" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="G31" s="64">
-        <v>1</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="L31" s="67"/>
-      <c r="V31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="X31" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y31" s="50" t="s">
-        <v>152</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="G9:G31">
+  <conditionalFormatting sqref="G9:G30">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
@@ -3458,21 +3453,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22 G9:G18 G26:G28 G31 G20" xr:uid="{EDC952CC-97B4-994F-AA14-28A44C65C7A2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G21 G25:G27 G30 G19 G9:G17" xr:uid="{EDC952CC-97B4-994F-AA14-28A44C65C7A2}">
       <formula1>"0..n, 0..1, 1, 1..n"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="D7" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="C30" r:id="rId3" location="Property:dataset_temporal_resolution" xr:uid="{F6F67CDC-7F97-2B4F-A5E8-1A7F7A804176}"/>
+    <hyperlink ref="C29" r:id="rId3" location="Property:dataset_temporal_resolution" xr:uid="{F6F67CDC-7F97-2B4F-A5E8-1A7F7A804176}"/>
     <hyperlink ref="C10" r:id="rId4" location="Property:distribution_accessurl" xr:uid="{DD921561-5282-EC4F-A210-6BA7C3349004}"/>
-    <hyperlink ref="C21" r:id="rId5" location="terms-license" xr:uid="{3E72892B-FB76-A148-AD80-8A2C3BB661EF}"/>
+    <hyperlink ref="C20" r:id="rId5" location="terms-license" xr:uid="{3E72892B-FB76-A148-AD80-8A2C3BB661EF}"/>
     <hyperlink ref="C9" r:id="rId6" location="Property:distribution_access_service" xr:uid="{7014D47C-FDE8-0848-841B-F43477897867}"/>
-    <hyperlink ref="C26" r:id="rId7" location="terms-issued" xr:uid="{D9C9DF0C-74FB-D643-A641-3F9D78AC19C9}"/>
-    <hyperlink ref="C28" r:id="rId8" location="terms-rights" xr:uid="{7F73E49C-32B2-4546-80F3-40E53493DB21}"/>
-    <hyperlink ref="M27" r:id="rId9" xr:uid="{23825230-1AB2-4ED6-9AE5-2BD6C1DA90D5}"/>
-    <hyperlink ref="M14" r:id="rId10" xr:uid="{2ED09ADA-EEB6-40CA-8B1E-539BBBACEB39}"/>
+    <hyperlink ref="C25" r:id="rId7" location="terms-issued" xr:uid="{D9C9DF0C-74FB-D643-A641-3F9D78AC19C9}"/>
+    <hyperlink ref="C27" r:id="rId8" location="terms-rights" xr:uid="{7F73E49C-32B2-4546-80F3-40E53493DB21}"/>
+    <hyperlink ref="M26" r:id="rId9" xr:uid="{23825230-1AB2-4ED6-9AE5-2BD6C1DA90D5}"/>
+    <hyperlink ref="M13" r:id="rId10" xr:uid="{2ED09ADA-EEB6-40CA-8B1E-539BBBACEB39}"/>
+    <hyperlink ref="M27" r:id="rId11" xr:uid="{6B829B85-551A-4E3A-A457-98D65EBE535B}"/>
   </hyperlinks>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.05277777777778" bottom="1.05277777777778" header="0.78750000000000009" footer="0.78750000000000009"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3484,6 +3480,36 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
+    <Categorie xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
+    <Persoon xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Persoon>
+    <Opmerkingen xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="31f6c59cfd598d1d7de5b45c1822abcd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="67714481eaab3d0eef8b708c465ce66d" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -3771,51 +3797,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
-    <Categorie xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
-    <Persoon xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Persoon>
-    <Opmerkingen xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228A4FD4-9C74-4788-AC27-9C2192995994}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF0D4BE-F0F3-4B03-A8BD-9CD4C60B556D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
-    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3838,9 +3823,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF0D4BE-F0F3-4B03-A8BD-9CD4C60B556D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228A4FD4-9C74-4788-AC27-9C2192995994}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
+    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>